--- a/02_Zero_Shot/outputs/Embedding/MiniLM/RESULT_f-droid_minilm_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/MiniLM/RESULT_f-droid_minilm_zeroshot.xlsx
@@ -48806,7 +48806,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6779802152183528</v>
+        <v>0.6779802152183529</v>
       </c>
     </row>
     <row r="5">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.883874698</v>
+        <v>23.98715661599999</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001015091410770855</v>
+        <v>0.008443208946145721</v>
       </c>
     </row>
   </sheetData>
